--- a/Sheets/One-Shot Premades/Fortaleza.xlsx
+++ b/Sheets/One-Shot Premades/Fortaleza.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Javier\TTRPGs\Marvel Multiverse\Sheets\One-Shot Premades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Javier\TTRPGs\Marvel Multiverse RPG\Sheets\One-Shot Premades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34918946-072C-4EA8-9887-264A7C860575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A0AE6F-0E03-4360-883B-16C32178F8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frente" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>Melee</t>
   </si>
@@ -236,28 +236,13 @@
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>+1 Melé  1 Agilidad</t>
-  </si>
-  <si>
     <t>Melé</t>
   </si>
   <si>
     <t>Tot. 10</t>
   </si>
   <si>
-    <t>Aplastar (Estándar, Instantáneo + 1 Ronda)</t>
-  </si>
-  <si>
     <t>Inamovible (Permanente)</t>
-  </si>
-  <si>
-    <t>Sos tratado como Enorme al levantar, empujar y arrastar objetos o personas.</t>
-  </si>
-  <si>
-    <t>Montracargas 2 (Permanente)</t>
-  </si>
-  <si>
-    <t>Ataque de Melé vs Defensa de Melé a alcanze. En un éxito, daño normal. Si es Fantástico, doble daño y el objetivo esta Aturdido por una ronda.</t>
   </si>
   <si>
     <r>
@@ -323,15 +308,9 @@
     <t>Poderoso (Permanente)</t>
   </si>
   <si>
-    <t>Tienes un +1 a tu Multiplicador de Daño de Melee.</t>
-  </si>
-  <si>
     <t>Rompetierras (Estándar, Instantáneo, 5+ Foco)</t>
   </si>
   <si>
-    <t>Al usar un poder de Super Fuerza que haga daño, incrementa el daño en 1 por cada 2 Foco gastado.</t>
-  </si>
-  <si>
     <t>Robustez (Permanente)</t>
   </si>
   <si>
@@ -348,9 +327,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tienes una velocidad de </t>
-  </si>
-  <si>
-    <t>Aplastar, Saltar, Montacargas 2</t>
   </si>
   <si>
     <r>
@@ -393,30 +369,6 @@
       </rPr>
       <t>Robustez, Reflejos de Batalla</t>
     </r>
-  </si>
-  <si>
-    <t>Tienes Daño de Reducción de Aguante 1</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Básico: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Poderoso</t>
-    </r>
-  </si>
-  <si>
-    <t>Rompemoldes (Gratis, Instantáneo, 5+ Foco)</t>
-  </si>
-  <si>
-    <t>Ataque de Melé vs Defensa de Melé hacia todos los enemigos a alcance + Grado. En un éxito, mitad daño. Si es Fantástico, daño normal y el objetivo esta Aturdido y Tumbado por una ronda.</t>
   </si>
   <si>
     <r>
@@ -463,7 +415,67 @@
     </r>
   </si>
   <si>
-    <t>Cuando sos empujado, la distancia que te empujan es reducida por 5 + tu Melé.</t>
+    <t>Poderoso</t>
+  </si>
+  <si>
+    <t>Aplastar, Saltar, Montacargas</t>
+  </si>
+  <si>
+    <t>Aplastar (Estándar, Instantáneo)</t>
+  </si>
+  <si>
+    <t>Tienes un +1 a tu Multiplicador de Daño Melé.</t>
+  </si>
+  <si>
+    <t>Tienes Daño de Reducción de Aguante 1.</t>
+  </si>
+  <si>
+    <t>Cuando sos empujado, la distancia que te empujan es reducida por tu Melé x 2.</t>
+  </si>
+  <si>
+    <t>Al usar un poder de Super Fuerza que haga daño, puedes gastar 5 o mas Foco e incrementar el daño en 1 por cada 2 Foco gastado.</t>
+  </si>
+  <si>
+    <t>Ataque de Melé vs Defensa de Melé hacia todos los enemigos a alcance + Grado. En un éxito, mitad daño de Aguante. Si es Fantástico, daño normal y el objetivo esta Aturdido y Tumbado por una ronda.</t>
+  </si>
+  <si>
+    <t>Rompemoldes (Permanente, 5+ Foco)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Artes Marciales: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Postura de Ataque</t>
+    </r>
+  </si>
+  <si>
+    <t>El primer Ataque que realizas en cada turno vs Defensa de Melé o Agilidad tiene Ventaja.</t>
+  </si>
+  <si>
+    <t>Básico</t>
+  </si>
+  <si>
+    <t>Montacargas (Permanente)</t>
+  </si>
+  <si>
+    <t>Sos tratado como Grande al levantar, empujar y arrastrar objetos o personas.</t>
+  </si>
+  <si>
+    <t>Ataque de Melé vs Defensa de Melé a alcance. En un éxito, daño normal de Aguante. Si es Fantástico, doble daño y el objetivo esta Aturdido por una ronda.</t>
+  </si>
+  <si>
+    <t>Postura de Ataque (Estándar o Movimiento, Concentración, 5 Foco)</t>
+  </si>
+  <si>
+    <t>+1 Melé  +1 Resiliencia</t>
   </si>
 </sst>
 </file>
@@ -1534,7 +1546,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="266">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1643,7 +1655,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1661,9 +1672,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1678,9 +1686,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1695,9 +1700,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1725,6 +1727,20 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="70" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="71" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1809,6 +1825,18 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1821,15 +1849,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1899,8 +1918,29 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1928,24 +1968,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2059,6 +2081,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2076,15 +2107,6 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2103,6 +2125,33 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2113,31 +2162,73 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="42" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="39" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="43" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2145,59 +2236,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="42" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="39" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="43" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2214,19 +2257,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2613,19 +2643,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="e" vm="1">
+      <c r="A1" s="126" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
       <c r="F1" s="23"/>
       <c r="G1" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="164"/>
-      <c r="I1" s="165"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="171"/>
       <c r="K1" s="39" t="s">
         <v>38</v>
       </c>
@@ -2633,51 +2663,51 @@
       <c r="N1" s="23"/>
     </row>
     <row r="2" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="118"/>
-      <c r="B2" s="118"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
+      <c r="A2" s="126"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="166" t="s">
+      <c r="G2" s="172" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="168"/>
-      <c r="I2" s="169"/>
-      <c r="K2" s="178" t="s">
+      <c r="H2" s="174"/>
+      <c r="I2" s="175"/>
+      <c r="K2" s="184" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="179"/>
-      <c r="M2" s="180"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="186"/>
     </row>
     <row r="3" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="167"/>
-      <c r="H3" s="170"/>
-      <c r="I3" s="171"/>
-      <c r="K3" s="107" t="s">
+      <c r="G3" s="173"/>
+      <c r="H3" s="176"/>
+      <c r="I3" s="177"/>
+      <c r="K3" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="108"/>
-      <c r="M3" s="109"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="113"/>
     </row>
     <row r="4" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="118"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
       <c r="F4" s="23"/>
-      <c r="G4" s="166" t="s">
+      <c r="G4" s="172" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="168"/>
-      <c r="I4" s="169"/>
+      <c r="H4" s="174"/>
+      <c r="I4" s="175"/>
       <c r="K4" s="40" t="s">
         <v>46</v>
       </c>
@@ -2685,19 +2715,19 @@
       <c r="M4" s="30"/>
     </row>
     <row r="5" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="93" t="s">
+      <c r="B5" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="93"/>
-      <c r="D5" s="94"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="98"/>
       <c r="E5" s="46"/>
       <c r="F5" s="23"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="170"/>
-      <c r="I5" s="171"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="176"/>
+      <c r="I5" s="177"/>
       <c r="K5" s="49" t="s">
         <v>47</v>
       </c>
@@ -2709,21 +2739,21 @@
       <c r="G6" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="164" t="s">
+      <c r="H6" s="170" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="165"/>
-      <c r="K6" s="172"/>
-      <c r="L6" s="173"/>
-      <c r="M6" s="174"/>
+      <c r="I6" s="171"/>
+      <c r="K6" s="178"/>
+      <c r="L6" s="179"/>
+      <c r="M6" s="180"/>
     </row>
     <row r="7" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="115" t="s">
+      <c r="A7" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="117"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="121"/>
       <c r="E7" s="27" t="s">
         <v>40</v>
       </c>
@@ -2731,19 +2761,19 @@
       <c r="G7" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="164"/>
-      <c r="I7" s="165"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="108"/>
-      <c r="M7" s="109"/>
+      <c r="H7" s="170"/>
+      <c r="I7" s="171"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="112"/>
+      <c r="M7" s="113"/>
       <c r="U7" s="23"/>
       <c r="V7" s="23"/>
     </row>
     <row r="8" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="145"/>
-      <c r="B8" s="146"/>
-      <c r="C8" s="146"/>
-      <c r="D8" s="147"/>
+      <c r="A8" s="150"/>
+      <c r="B8" s="151"/>
+      <c r="C8" s="151"/>
+      <c r="D8" s="152"/>
       <c r="E8" s="28">
         <v>1</v>
       </c>
@@ -2751,13 +2781,13 @@
       <c r="G8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="164" t="s">
+      <c r="H8" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="165"/>
-      <c r="K8" s="107"/>
-      <c r="L8" s="108"/>
-      <c r="M8" s="109"/>
+      <c r="I8" s="171"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="113"/>
     </row>
     <row r="9" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="23"/>
@@ -2766,62 +2796,62 @@
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
-      <c r="K9" s="107"/>
-      <c r="L9" s="108"/>
-      <c r="M9" s="109"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="112"/>
+      <c r="M9" s="113"/>
     </row>
     <row r="10" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="125" t="s">
+      <c r="A10" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="130" t="s">
         <v>30</v>
       </c>
       <c r="F10" s="23"/>
-      <c r="G10" s="181" t="s">
+      <c r="G10" s="187" t="s">
         <v>42</v>
       </c>
-      <c r="H10" s="182"/>
-      <c r="I10" s="183"/>
-      <c r="K10" s="175"/>
-      <c r="L10" s="176"/>
-      <c r="M10" s="177"/>
+      <c r="H10" s="188"/>
+      <c r="I10" s="189"/>
+      <c r="K10" s="181"/>
+      <c r="L10" s="182"/>
+      <c r="M10" s="183"/>
     </row>
     <row r="11" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="184" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="185"/>
-      <c r="C11" s="185"/>
-      <c r="D11" s="186"/>
-      <c r="E11" s="126"/>
+      <c r="A11" s="190" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="191"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="192"/>
+      <c r="E11" s="131"/>
       <c r="F11" s="23"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="196"/>
-      <c r="I11" s="197"/>
-      <c r="K11" s="192"/>
-      <c r="L11" s="193"/>
-      <c r="M11" s="194"/>
+      <c r="G11" s="201"/>
+      <c r="H11" s="202"/>
+      <c r="I11" s="203"/>
+      <c r="K11" s="198"/>
+      <c r="L11" s="199"/>
+      <c r="M11" s="200"/>
     </row>
     <row r="12" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="129"/>
-      <c r="B12" s="130"/>
-      <c r="C12" s="88" t="str">
+      <c r="A12" s="134"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="92" t="str">
         <f>_xlfn.CONCAT("/",IF(A32=0,20,20 + A32*IF(Modifiers!O5,Modifiers!O5,20)) + Modifiers!N5)</f>
         <v>/60</v>
       </c>
-      <c r="D12" s="89"/>
+      <c r="D12" s="93"/>
       <c r="E12" s="24"/>
       <c r="F12" s="23"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="97"/>
-      <c r="K12" s="107"/>
-      <c r="L12" s="108"/>
-      <c r="M12" s="109"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="101"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="113"/>
     </row>
     <row r="13" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23"/>
@@ -2830,63 +2860,63 @@
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="97"/>
-      <c r="K13" s="107"/>
-      <c r="L13" s="108"/>
-      <c r="M13" s="109"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="101"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="113"/>
     </row>
     <row r="14" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="125" t="s">
+      <c r="A14" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="130" t="s">
         <v>30</v>
       </c>
       <c r="F14" s="23"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="97"/>
-      <c r="K14" s="107"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="109"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="101"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="113"/>
     </row>
     <row r="15" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="184" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="185"/>
-      <c r="C15" s="185"/>
-      <c r="D15" s="186"/>
-      <c r="E15" s="126"/>
+      <c r="A15" s="190" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="191"/>
+      <c r="C15" s="191"/>
+      <c r="D15" s="192"/>
+      <c r="E15" s="131"/>
       <c r="F15" s="23"/>
-      <c r="G15" s="198"/>
-      <c r="H15" s="199"/>
-      <c r="I15" s="200"/>
-      <c r="K15" s="107"/>
-      <c r="L15" s="108"/>
-      <c r="M15" s="109"/>
+      <c r="G15" s="204"/>
+      <c r="H15" s="205"/>
+      <c r="I15" s="206"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="113"/>
     </row>
     <row r="16" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="129"/>
-      <c r="B16" s="130"/>
-      <c r="C16" s="88" t="str">
+      <c r="A16" s="134"/>
+      <c r="B16" s="135"/>
+      <c r="C16" s="92" t="str">
         <f>_xlfn.CONCAT("/",IF(A34=0,20,20 + A34 * IF(Modifiers!O6,Modifiers!O6,20)) + Modifiers!N6)</f>
         <v>/20</v>
       </c>
-      <c r="D16" s="89"/>
+      <c r="D16" s="93"/>
       <c r="E16" s="24"/>
       <c r="F16" s="23"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="97"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="108"/>
-      <c r="M16" s="109"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="101"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="113"/>
     </row>
     <row r="17" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23"/>
@@ -2895,88 +2925,88 @@
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="97"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="108"/>
-      <c r="M17" s="109"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="101"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="113"/>
     </row>
     <row r="18" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="140"/>
-      <c r="E18" s="125" t="s">
+      <c r="A18" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="64"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="130" t="s">
         <v>31</v>
       </c>
       <c r="F18" s="23"/>
-      <c r="G18" s="101"/>
-      <c r="H18" s="102"/>
-      <c r="I18" s="103"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="108"/>
-      <c r="M18" s="109"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="107"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="113"/>
     </row>
     <row r="19" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="187" t="s">
+      <c r="A19" s="193" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="188"/>
-      <c r="C19" s="189"/>
-      <c r="D19" s="141"/>
-      <c r="E19" s="126"/>
+      <c r="B19" s="194"/>
+      <c r="C19" s="195"/>
+      <c r="D19" s="146"/>
+      <c r="E19" s="131"/>
       <c r="F19" s="23"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="99"/>
-      <c r="I19" s="100"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="109"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="104"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="113"/>
     </row>
     <row r="20" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="155" t="s">
+      <c r="A20" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="156"/>
-      <c r="C20" s="156"/>
-      <c r="D20" s="157"/>
+      <c r="B20" s="168"/>
+      <c r="C20" s="168"/>
+      <c r="D20" s="169"/>
       <c r="E20" s="25" t="str">
         <f>_xlfn.CONCAT("+",IF(Modifiers!K6="Edge",_xlfn.CONCAT(A34,"E"),A34))</f>
         <v>+0</v>
       </c>
       <c r="F20" s="23"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="97"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="108"/>
-      <c r="M20" s="109"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="101"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="113"/>
     </row>
     <row r="21" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="142" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="143"/>
-      <c r="C21" s="143"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="144"/>
+      <c r="A21" s="147" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="148"/>
+      <c r="C21" s="148"/>
+      <c r="D21" s="148"/>
+      <c r="E21" s="149"/>
       <c r="F21" s="23"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="106"/>
-      <c r="K21" s="112"/>
-      <c r="L21" s="113"/>
-      <c r="M21" s="114"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="110"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="118"/>
     </row>
     <row r="22" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="142"/>
-      <c r="B22" s="143"/>
-      <c r="C22" s="143"/>
-      <c r="D22" s="143"/>
-      <c r="E22" s="151"/>
+      <c r="A22" s="147"/>
+      <c r="B22" s="148"/>
+      <c r="C22" s="148"/>
+      <c r="D22" s="148"/>
+      <c r="E22" s="163"/>
       <c r="F22" s="23"/>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
@@ -2985,13 +3015,13 @@
       <c r="N22" s="23"/>
     </row>
     <row r="23" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="149"/>
-      <c r="B23" s="150"/>
-      <c r="C23" s="146"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="147"/>
+      <c r="A23" s="161"/>
+      <c r="B23" s="162"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="151"/>
+      <c r="E23" s="152"/>
       <c r="F23" s="23"/>
-      <c r="G23" s="56" t="s">
+      <c r="G23" s="55" t="s">
         <v>17</v>
       </c>
       <c r="H23" s="23"/>
@@ -3010,116 +3040,120 @@
       <c r="E24" s="23"/>
       <c r="F24" s="23"/>
       <c r="G24" s="35" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="H24" s="36"/>
-      <c r="I24" s="190" t="s">
+      <c r="I24" s="196" t="s">
         <v>78</v>
       </c>
-      <c r="J24" s="190"/>
-      <c r="K24" s="190"/>
-      <c r="L24" s="190"/>
-      <c r="M24" s="191"/>
+      <c r="J24" s="196"/>
+      <c r="K24" s="196"/>
+      <c r="L24" s="196"/>
+      <c r="M24" s="197"/>
     </row>
     <row r="25" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="152" t="s">
+      <c r="A25" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="153"/>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="154"/>
+      <c r="B25" s="165"/>
+      <c r="C25" s="165"/>
+      <c r="D25" s="165"/>
+      <c r="E25" s="166"/>
       <c r="F25" s="23"/>
       <c r="G25" s="37"/>
       <c r="H25" s="38"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="110"/>
-      <c r="L25" s="110"/>
-      <c r="M25" s="111"/>
+      <c r="I25" s="114"/>
+      <c r="J25" s="114"/>
+      <c r="K25" s="114"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="115"/>
     </row>
     <row r="26" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="134" t="s">
+      <c r="A26" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="135"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="135" t="s">
+      <c r="B26" s="140"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="138"/>
+      <c r="E26" s="143"/>
       <c r="F26" s="23"/>
       <c r="G26" s="37"/>
       <c r="H26" s="38"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="110"/>
-      <c r="L26" s="110"/>
-      <c r="M26" s="111"/>
+      <c r="I26" s="114"/>
+      <c r="J26" s="114"/>
+      <c r="K26" s="114"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="115"/>
     </row>
     <row r="27" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="136"/>
-      <c r="B27" s="137"/>
-      <c r="C27" s="137"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="37"/>
+      <c r="A27" s="141"/>
+      <c r="B27" s="142"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="142"/>
+      <c r="E27" s="144"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="37" t="s">
+        <v>48</v>
+      </c>
       <c r="H27" s="38"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="110"/>
-      <c r="L27" s="110"/>
-      <c r="M27" s="111"/>
+      <c r="I27" s="114" t="s">
+        <v>79</v>
+      </c>
+      <c r="J27" s="114"/>
+      <c r="K27" s="114"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="115"/>
     </row>
     <row r="28" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="131">
+      <c r="A28" s="136">
         <v>2</v>
       </c>
-      <c r="B28" s="132"/>
-      <c r="C28" s="133"/>
-      <c r="D28" s="119">
+      <c r="B28" s="137"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="127">
         <f xml:space="preserve"> 10 + A28 + Modifiers!B3</f>
         <v>12</v>
       </c>
-      <c r="E28" s="121"/>
-      <c r="F28" s="23"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="83"/>
       <c r="G28" s="37"/>
       <c r="H28" s="38"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="111"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="115"/>
     </row>
     <row r="29" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="122" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="123"/>
-      <c r="C29" s="124"/>
-      <c r="D29" s="127"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="23"/>
+      <c r="A29" s="123" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="124"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="83"/>
       <c r="G29" s="37"/>
       <c r="H29" s="38"/>
-      <c r="I29" s="110"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="110"/>
-      <c r="L29" s="110"/>
-      <c r="M29" s="111"/>
+      <c r="I29" s="114"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="114"/>
+      <c r="L29" s="114"/>
+      <c r="M29" s="115"/>
     </row>
     <row r="30" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="131">
+      <c r="A30" s="136">
         <v>1</v>
       </c>
-      <c r="B30" s="132"/>
-      <c r="C30" s="133"/>
-      <c r="D30" s="119">
+      <c r="B30" s="137"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="127">
         <f>IF(Modifiers!C4,Modifiers!C4,10 + A30 + Modifiers!B4)</f>
         <v>11</v>
       </c>
-      <c r="E30" s="121"/>
+      <c r="E30" s="129"/>
       <c r="F30" s="23"/>
       <c r="G30" s="37"/>
       <c r="H30" s="38"/>
@@ -3130,13 +3164,13 @@
       <c r="M30" s="30"/>
     </row>
     <row r="31" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="122" t="s">
+      <c r="A31" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="123"/>
-      <c r="C31" s="124"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="128"/>
+      <c r="B31" s="124"/>
+      <c r="C31" s="125"/>
+      <c r="D31" s="132"/>
+      <c r="E31" s="133"/>
       <c r="F31" s="23"/>
       <c r="G31" s="37"/>
       <c r="H31" s="38"/>
@@ -3147,16 +3181,16 @@
       <c r="M31" s="30"/>
     </row>
     <row r="32" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="131">
+      <c r="A32" s="136">
         <v>2</v>
       </c>
-      <c r="B32" s="132"/>
-      <c r="C32" s="133"/>
-      <c r="D32" s="119">
+      <c r="B32" s="137"/>
+      <c r="C32" s="138"/>
+      <c r="D32" s="127">
         <f xml:space="preserve"> 10 + A32 + Modifiers!B5</f>
         <v>12</v>
       </c>
-      <c r="E32" s="121"/>
+      <c r="E32" s="129"/>
       <c r="F32" s="23"/>
       <c r="G32" s="37"/>
       <c r="H32" s="38"/>
@@ -3167,13 +3201,13 @@
       <c r="M32" s="30"/>
     </row>
     <row r="33" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="122" t="s">
+      <c r="A33" s="123" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="123"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="128"/>
+      <c r="B33" s="124"/>
+      <c r="C33" s="125"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="133"/>
       <c r="F33" s="23"/>
       <c r="G33" s="37"/>
       <c r="H33" s="38"/>
@@ -3184,16 +3218,16 @@
       <c r="M33" s="30"/>
     </row>
     <row r="34" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="131">
+      <c r="A34" s="136">
         <v>0</v>
       </c>
-      <c r="B34" s="132"/>
-      <c r="C34" s="133"/>
-      <c r="D34" s="119">
+      <c r="B34" s="137"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="127">
         <f xml:space="preserve"> 10 + A34 + Modifiers!B6</f>
         <v>10</v>
       </c>
-      <c r="E34" s="121"/>
+      <c r="E34" s="129"/>
       <c r="F34" s="23"/>
       <c r="G34" s="37"/>
       <c r="H34" s="38"/>
@@ -3204,13 +3238,13 @@
       <c r="M34" s="30"/>
     </row>
     <row r="35" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="122" t="s">
+      <c r="A35" s="123" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="123"/>
-      <c r="C35" s="124"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="128"/>
+      <c r="B35" s="124"/>
+      <c r="C35" s="125"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="133"/>
       <c r="F35" s="23"/>
       <c r="G35" s="37"/>
       <c r="H35" s="38"/>
@@ -3221,16 +3255,16 @@
       <c r="M35" s="30"/>
     </row>
     <row r="36" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="131">
+      <c r="A36" s="136">
         <v>1</v>
       </c>
-      <c r="B36" s="132"/>
-      <c r="C36" s="133"/>
-      <c r="D36" s="119">
+      <c r="B36" s="137"/>
+      <c r="C36" s="138"/>
+      <c r="D36" s="127">
         <f xml:space="preserve"> 10 + A36 + Modifiers!B7</f>
         <v>11</v>
       </c>
-      <c r="E36" s="121"/>
+      <c r="E36" s="129"/>
       <c r="F36" s="23"/>
       <c r="G36" s="37"/>
       <c r="H36" s="38"/>
@@ -3241,13 +3275,13 @@
       <c r="M36" s="30"/>
     </row>
     <row r="37" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="122" t="s">
+      <c r="A37" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="123"/>
-      <c r="C37" s="124"/>
-      <c r="D37" s="127"/>
-      <c r="E37" s="128"/>
+      <c r="B37" s="124"/>
+      <c r="C37" s="125"/>
+      <c r="D37" s="132"/>
+      <c r="E37" s="133"/>
       <c r="F37" s="23"/>
       <c r="G37" s="37"/>
       <c r="H37" s="38"/>
@@ -3258,16 +3292,16 @@
       <c r="M37" s="30"/>
     </row>
     <row r="38" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="119">
+      <c r="A38" s="127">
         <v>0</v>
       </c>
-      <c r="B38" s="120"/>
-      <c r="C38" s="121"/>
-      <c r="D38" s="119">
+      <c r="B38" s="128"/>
+      <c r="C38" s="129"/>
+      <c r="D38" s="127">
         <f xml:space="preserve"> 10 + A38 + Modifiers!B8</f>
         <v>10</v>
       </c>
-      <c r="E38" s="121"/>
+      <c r="E38" s="129"/>
       <c r="F38" s="23"/>
       <c r="G38" s="37"/>
       <c r="H38" s="38"/>
@@ -3278,13 +3312,13 @@
       <c r="M38" s="30"/>
     </row>
     <row r="39" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="122" t="s">
+      <c r="A39" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="123"/>
-      <c r="C39" s="124"/>
-      <c r="D39" s="127"/>
-      <c r="E39" s="128"/>
+      <c r="B39" s="124"/>
+      <c r="C39" s="125"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="133"/>
       <c r="F39" s="23"/>
       <c r="G39" s="37"/>
       <c r="H39" s="38"/>
@@ -3301,22 +3335,22 @@
       <c r="D40" s="23"/>
       <c r="E40" s="23"/>
       <c r="F40" s="23"/>
-      <c r="G40" s="90"/>
-      <c r="H40" s="91"/>
-      <c r="I40" s="91"/>
-      <c r="J40" s="91"/>
-      <c r="K40" s="91"/>
-      <c r="L40" s="91"/>
-      <c r="M40" s="92"/>
+      <c r="G40" s="94"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="95"/>
+      <c r="J40" s="95"/>
+      <c r="K40" s="95"/>
+      <c r="L40" s="95"/>
+      <c r="M40" s="96"/>
     </row>
     <row r="41" spans="1:14" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="158" t="s">
+      <c r="A41" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="B41" s="159"/>
-      <c r="C41" s="159"/>
-      <c r="D41" s="159"/>
-      <c r="E41" s="160"/>
+      <c r="B41" s="155"/>
+      <c r="C41" s="155"/>
+      <c r="D41" s="155"/>
+      <c r="E41" s="156"/>
       <c r="F41" s="23"/>
       <c r="G41" s="23"/>
       <c r="H41" s="23"/>
@@ -3327,20 +3361,20 @@
       <c r="M41" s="23"/>
     </row>
     <row r="42" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="148" t="s">
-        <v>52</v>
-      </c>
-      <c r="B42" s="263" t="e" vm="2">
+      <c r="A42" s="122" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="153" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C42" s="264" t="str">
+      <c r="C42" s="157" t="str">
         <f>_xlfn.CONCAT("X ",IF(Modifiers!G3,Modifiers!G3,$E$8 + Modifiers!F3))</f>
-        <v>X 1</v>
-      </c>
-      <c r="D42" s="163" t="s">
+        <v>X 2</v>
+      </c>
+      <c r="D42" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="E42" s="161">
+      <c r="E42" s="158">
         <f>A28</f>
         <v>2</v>
       </c>
@@ -3356,11 +3390,11 @@
       <c r="M42" s="23"/>
     </row>
     <row r="43" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="148"/>
-      <c r="B43" s="263"/>
-      <c r="C43" s="264"/>
-      <c r="D43" s="162"/>
-      <c r="E43" s="161"/>
+      <c r="A43" s="122"/>
+      <c r="B43" s="153"/>
+      <c r="C43" s="157"/>
+      <c r="D43" s="159"/>
+      <c r="E43" s="158"/>
       <c r="F43" s="23"/>
       <c r="G43" s="41"/>
       <c r="H43" s="42"/>
@@ -3371,20 +3405,20 @@
       <c r="M43" s="43"/>
     </row>
     <row r="44" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="148" t="s">
+      <c r="A44" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="263" t="e" vm="3">
+      <c r="B44" s="153" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="C44" s="264" t="str">
+      <c r="C44" s="157" t="str">
         <f>_xlfn.CONCAT("X ",IF(Modifiers!G5,Modifiers!G5,$E$8 + Modifiers!F5))</f>
         <v>X 1</v>
       </c>
-      <c r="D44" s="162" t="s">
+      <c r="D44" s="159" t="s">
         <v>6</v>
       </c>
-      <c r="E44" s="161">
+      <c r="E44" s="158">
         <f>A30</f>
         <v>1</v>
       </c>
@@ -3398,12 +3432,12 @@
       <c r="M44" s="44"/>
     </row>
     <row r="45" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="148"/>
-      <c r="B45" s="263"/>
-      <c r="C45" s="264"/>
-      <c r="D45" s="162"/>
-      <c r="E45" s="161"/>
-      <c r="F45" s="265"/>
+      <c r="A45" s="122"/>
+      <c r="B45" s="153"/>
+      <c r="C45" s="157"/>
+      <c r="D45" s="159"/>
+      <c r="E45" s="158"/>
+      <c r="F45" s="82"/>
       <c r="G45" s="31"/>
       <c r="H45" s="29"/>
       <c r="I45" s="29"/>
@@ -3414,20 +3448,20 @@
       <c r="N45" s="23"/>
     </row>
     <row r="46" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="148" t="s">
+      <c r="A46" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="263" t="e" vm="3">
+      <c r="B46" s="153" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="C46" s="264" t="str">
+      <c r="C46" s="157" t="str">
         <f>_xlfn.CONCAT("X ",IF(Modifiers!G7,Modifiers!G7,$E$8 + Modifiers!F7))</f>
         <v>X 1</v>
       </c>
-      <c r="D46" s="162" t="s">
+      <c r="D46" s="159" t="s">
         <v>6</v>
       </c>
-      <c r="E46" s="161">
+      <c r="E46" s="158">
         <f>A36</f>
         <v>1</v>
       </c>
@@ -3442,61 +3476,61 @@
       <c r="N46" s="23"/>
     </row>
     <row r="47" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="148"/>
-      <c r="B47" s="263"/>
-      <c r="C47" s="264"/>
-      <c r="D47" s="162"/>
-      <c r="E47" s="161"/>
+      <c r="A47" s="122"/>
+      <c r="B47" s="153"/>
+      <c r="C47" s="157"/>
+      <c r="D47" s="159"/>
+      <c r="E47" s="158"/>
       <c r="F47" s="23"/>
-      <c r="G47" s="95"/>
-      <c r="H47" s="96"/>
-      <c r="I47" s="96"/>
-      <c r="J47" s="96"/>
-      <c r="K47" s="96"/>
-      <c r="L47" s="96"/>
-      <c r="M47" s="97"/>
+      <c r="G47" s="99"/>
+      <c r="H47" s="100"/>
+      <c r="I47" s="100"/>
+      <c r="J47" s="100"/>
+      <c r="K47" s="100"/>
+      <c r="L47" s="100"/>
+      <c r="M47" s="101"/>
     </row>
     <row r="48" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="148" t="s">
+      <c r="A48" s="122" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="263" t="e" vm="3">
+      <c r="B48" s="153" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="C48" s="264" t="str">
+      <c r="C48" s="157" t="str">
         <f>_xlfn.CONCAT("X ",IF(Modifiers!G9,Modifiers!G9,$E$8 + Modifiers!F9))</f>
         <v>X 1</v>
       </c>
-      <c r="D48" s="162" t="s">
+      <c r="D48" s="159" t="s">
         <v>6</v>
       </c>
-      <c r="E48" s="161">
+      <c r="E48" s="158">
         <f>A38</f>
         <v>0</v>
       </c>
       <c r="F48" s="23"/>
-      <c r="G48" s="95"/>
-      <c r="H48" s="96"/>
-      <c r="I48" s="96"/>
-      <c r="J48" s="96"/>
-      <c r="K48" s="96"/>
-      <c r="L48" s="96"/>
-      <c r="M48" s="97"/>
+      <c r="G48" s="99"/>
+      <c r="H48" s="100"/>
+      <c r="I48" s="100"/>
+      <c r="J48" s="100"/>
+      <c r="K48" s="100"/>
+      <c r="L48" s="100"/>
+      <c r="M48" s="101"/>
     </row>
     <row r="49" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="202"/>
-      <c r="B49" s="201"/>
-      <c r="C49" s="203"/>
-      <c r="D49" s="204"/>
-      <c r="E49" s="205"/>
+      <c r="A49" s="208"/>
+      <c r="B49" s="207"/>
+      <c r="C49" s="209"/>
+      <c r="D49" s="210"/>
+      <c r="E49" s="211"/>
       <c r="F49" s="23"/>
-      <c r="G49" s="95"/>
-      <c r="H49" s="96"/>
-      <c r="I49" s="96"/>
-      <c r="J49" s="96"/>
-      <c r="K49" s="96"/>
-      <c r="L49" s="96"/>
-      <c r="M49" s="97"/>
+      <c r="G49" s="99"/>
+      <c r="H49" s="100"/>
+      <c r="I49" s="100"/>
+      <c r="J49" s="100"/>
+      <c r="K49" s="100"/>
+      <c r="L49" s="100"/>
+      <c r="M49" s="101"/>
     </row>
     <row r="50" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="23"/>
@@ -3514,13 +3548,13 @@
       <c r="M50" s="30"/>
     </row>
     <row r="51" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="67"/>
-      <c r="C51" s="67"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="68"/>
+      <c r="A51" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="64"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="65"/>
       <c r="F51" s="23"/>
       <c r="G51" s="37"/>
       <c r="H51" s="38"/>
@@ -3531,13 +3565,13 @@
       <c r="M51" s="30"/>
     </row>
     <row r="52" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="184" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52" s="185"/>
-      <c r="C52" s="185"/>
-      <c r="D52" s="185"/>
-      <c r="E52" s="186"/>
+      <c r="A52" s="190" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="191"/>
+      <c r="C52" s="191"/>
+      <c r="D52" s="191"/>
+      <c r="E52" s="192"/>
       <c r="F52" s="23"/>
       <c r="G52" s="37"/>
       <c r="H52" s="38"/>
@@ -3548,23 +3582,23 @@
       <c r="M52" s="30"/>
     </row>
     <row r="53" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="86"/>
-      <c r="B53" s="87"/>
-      <c r="C53" s="88" t="s">
+      <c r="A53" s="90"/>
+      <c r="B53" s="91"/>
+      <c r="C53" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="D53" s="89"/>
+      <c r="D53" s="93"/>
       <c r="E53" s="45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F53" s="23"/>
-      <c r="G53" s="90"/>
-      <c r="H53" s="91"/>
-      <c r="I53" s="91"/>
-      <c r="J53" s="91"/>
-      <c r="K53" s="91"/>
-      <c r="L53" s="91"/>
-      <c r="M53" s="92"/>
+      <c r="G53" s="94"/>
+      <c r="H53" s="95"/>
+      <c r="I53" s="95"/>
+      <c r="J53" s="95"/>
+      <c r="K53" s="95"/>
+      <c r="L53" s="95"/>
+      <c r="M53" s="96"/>
     </row>
     <row r="54" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F54" s="23"/>
@@ -3697,523 +3731,527 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="224" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="220"/>
+      <c r="B1" s="225"/>
+      <c r="C1" s="225"/>
+      <c r="D1" s="226"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="221"/>
-      <c r="B2" s="222"/>
-      <c r="C2" s="222"/>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
-      <c r="G2" s="222"/>
-      <c r="H2" s="222"/>
-      <c r="I2" s="223"/>
+      <c r="A2" s="227"/>
+      <c r="B2" s="228"/>
+      <c r="C2" s="228"/>
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="228"/>
+      <c r="H2" s="228"/>
+      <c r="I2" s="229"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="206"/>
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
-      <c r="I3" s="208"/>
+      <c r="A3" s="212"/>
+      <c r="B3" s="213"/>
+      <c r="C3" s="213"/>
+      <c r="D3" s="213"/>
+      <c r="E3" s="213"/>
+      <c r="F3" s="213"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="213"/>
+      <c r="I3" s="214"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="209"/>
-      <c r="B4" s="210"/>
-      <c r="C4" s="210"/>
-      <c r="D4" s="210"/>
-      <c r="E4" s="210"/>
-      <c r="F4" s="210"/>
-      <c r="G4" s="210"/>
-      <c r="H4" s="210"/>
-      <c r="I4" s="211"/>
+      <c r="A4" s="218"/>
+      <c r="B4" s="219"/>
+      <c r="C4" s="219"/>
+      <c r="D4" s="219"/>
+      <c r="E4" s="219"/>
+      <c r="F4" s="219"/>
+      <c r="G4" s="219"/>
+      <c r="H4" s="219"/>
+      <c r="I4" s="220"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="209"/>
-      <c r="B5" s="210"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="210"/>
-      <c r="E5" s="210"/>
-      <c r="F5" s="210"/>
-      <c r="G5" s="210"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="211"/>
+      <c r="A5" s="218"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="219"/>
+      <c r="E5" s="219"/>
+      <c r="F5" s="219"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="220"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="209"/>
-      <c r="B6" s="210"/>
-      <c r="C6" s="210"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="210"/>
-      <c r="F6" s="210"/>
-      <c r="G6" s="210"/>
-      <c r="H6" s="210"/>
-      <c r="I6" s="211"/>
-    </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="215"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
-      <c r="E7" s="216"/>
-      <c r="F7" s="216"/>
-      <c r="G7" s="216"/>
-      <c r="H7" s="216"/>
-      <c r="I7" s="217"/>
+      <c r="A6" s="218"/>
+      <c r="B6" s="219"/>
+      <c r="C6" s="219"/>
+      <c r="D6" s="219"/>
+      <c r="E6" s="219"/>
+      <c r="F6" s="219"/>
+      <c r="G6" s="219"/>
+      <c r="H6" s="219"/>
+      <c r="I6" s="220"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="218"/>
+      <c r="B7" s="219"/>
+      <c r="C7" s="219"/>
+      <c r="D7" s="219"/>
+      <c r="E7" s="219"/>
+      <c r="F7" s="219"/>
+      <c r="G7" s="219"/>
+      <c r="H7" s="219"/>
+      <c r="I7" s="220"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="48"/>
+      <c r="A8" s="236" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="237"/>
+      <c r="C8" s="237"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="237"/>
+      <c r="G8" s="237"/>
+      <c r="H8" s="237"/>
+      <c r="I8" s="238"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="227" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="228"/>
-      <c r="C9" s="228"/>
-      <c r="D9" s="228"/>
-      <c r="E9" s="228"/>
-      <c r="F9" s="228"/>
-      <c r="G9" s="228"/>
-      <c r="H9" s="228"/>
-      <c r="I9" s="229"/>
+      <c r="A9" s="230" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="231"/>
+      <c r="C9" s="231"/>
+      <c r="D9" s="231"/>
+      <c r="E9" s="231"/>
+      <c r="F9" s="231"/>
+      <c r="G9" s="231"/>
+      <c r="H9" s="231"/>
+      <c r="I9" s="232"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="230"/>
-      <c r="B10" s="231"/>
-      <c r="C10" s="231"/>
-      <c r="D10" s="231"/>
-      <c r="E10" s="231"/>
-      <c r="F10" s="231"/>
-      <c r="G10" s="231"/>
-      <c r="H10" s="231"/>
-      <c r="I10" s="232"/>
+      <c r="A10" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="58"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="233" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="234"/>
-      <c r="C11" s="234"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="234"/>
-      <c r="F11" s="234"/>
-      <c r="G11" s="234"/>
-      <c r="H11" s="234"/>
-      <c r="I11" s="235"/>
+      <c r="A11" s="215" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="216"/>
+      <c r="C11" s="216"/>
+      <c r="D11" s="216"/>
+      <c r="E11" s="216"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="216"/>
+      <c r="H11" s="216"/>
+      <c r="I11" s="217"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="227" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="228"/>
-      <c r="C12" s="228"/>
-      <c r="D12" s="228"/>
-      <c r="E12" s="228"/>
-      <c r="F12" s="228"/>
-      <c r="G12" s="228"/>
-      <c r="H12" s="228"/>
-      <c r="I12" s="229"/>
+      <c r="A12" s="230"/>
+      <c r="B12" s="231"/>
+      <c r="C12" s="231"/>
+      <c r="D12" s="231"/>
+      <c r="E12" s="231"/>
+      <c r="F12" s="231"/>
+      <c r="G12" s="231"/>
+      <c r="H12" s="231"/>
+      <c r="I12" s="232"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="230"/>
-      <c r="B13" s="231"/>
-      <c r="C13" s="231"/>
-      <c r="D13" s="231"/>
-      <c r="E13" s="231"/>
-      <c r="F13" s="231"/>
-      <c r="G13" s="231"/>
-      <c r="H13" s="231"/>
-      <c r="I13" s="232"/>
+      <c r="A13" s="233" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="234"/>
+      <c r="C13" s="234"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="234"/>
+      <c r="G13" s="234"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="235"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="212" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="213"/>
-      <c r="C14" s="213"/>
-      <c r="D14" s="213"/>
-      <c r="E14" s="213"/>
-      <c r="F14" s="213"/>
-      <c r="G14" s="213"/>
-      <c r="H14" s="213"/>
-      <c r="I14" s="214"/>
+      <c r="A14" s="215" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="216"/>
+      <c r="C14" s="216"/>
+      <c r="D14" s="216"/>
+      <c r="E14" s="216"/>
+      <c r="F14" s="216"/>
+      <c r="G14" s="216"/>
+      <c r="H14" s="216"/>
+      <c r="I14" s="217"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="227" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="228"/>
-      <c r="C15" s="228"/>
-      <c r="D15" s="228"/>
-      <c r="E15" s="228"/>
-      <c r="F15" s="228"/>
-      <c r="G15" s="228"/>
-      <c r="H15" s="228"/>
-      <c r="I15" s="229"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="231"/>
+      <c r="D15" s="231"/>
+      <c r="E15" s="231"/>
+      <c r="F15" s="231"/>
+      <c r="G15" s="231"/>
+      <c r="H15" s="231"/>
+      <c r="I15" s="232"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="57"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="59"/>
+      <c r="A16" s="221" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="222"/>
+      <c r="C16" s="222"/>
+      <c r="D16" s="222"/>
+      <c r="E16" s="222"/>
+      <c r="F16" s="222"/>
+      <c r="G16" s="222"/>
+      <c r="H16" s="222"/>
+      <c r="I16" s="223"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="57"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="59"/>
+      <c r="A17" s="215" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="216"/>
+      <c r="C17" s="216"/>
+      <c r="D17" s="216"/>
+      <c r="E17" s="216"/>
+      <c r="F17" s="216"/>
+      <c r="G17" s="216"/>
+      <c r="H17" s="216"/>
+      <c r="I17" s="217"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="57"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="59"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="85"/>
+      <c r="I18" s="57"/>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="59"/>
+      <c r="A19" s="56"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="85"/>
+      <c r="I19" s="57"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="57"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="59"/>
+      <c r="A20" s="56"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="57"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="57"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="59"/>
+      <c r="A21" s="56"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="57"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="57"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="59"/>
+      <c r="A22" s="56"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="57"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="57"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="59"/>
+      <c r="A23" s="56"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="57"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
-      <c r="B24" s="207"/>
-      <c r="C24" s="207"/>
-      <c r="D24" s="207"/>
-      <c r="E24" s="207"/>
-      <c r="F24" s="207"/>
-      <c r="G24" s="207"/>
-      <c r="H24" s="207"/>
-      <c r="I24" s="208"/>
+      <c r="A24" s="212"/>
+      <c r="B24" s="213"/>
+      <c r="C24" s="213"/>
+      <c r="D24" s="213"/>
+      <c r="E24" s="213"/>
+      <c r="F24" s="213"/>
+      <c r="G24" s="213"/>
+      <c r="H24" s="213"/>
+      <c r="I24" s="214"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="206"/>
-      <c r="B25" s="207"/>
-      <c r="C25" s="207"/>
-      <c r="D25" s="207"/>
-      <c r="E25" s="207"/>
-      <c r="F25" s="207"/>
-      <c r="G25" s="207"/>
-      <c r="H25" s="207"/>
-      <c r="I25" s="208"/>
+      <c r="A25" s="212"/>
+      <c r="B25" s="213"/>
+      <c r="C25" s="213"/>
+      <c r="D25" s="213"/>
+      <c r="E25" s="213"/>
+      <c r="F25" s="213"/>
+      <c r="G25" s="213"/>
+      <c r="H25" s="213"/>
+      <c r="I25" s="214"/>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="206"/>
-      <c r="B26" s="207"/>
-      <c r="C26" s="207"/>
-      <c r="D26" s="207"/>
-      <c r="E26" s="207"/>
-      <c r="F26" s="207"/>
-      <c r="G26" s="207"/>
-      <c r="H26" s="207"/>
-      <c r="I26" s="208"/>
+      <c r="A26" s="212"/>
+      <c r="B26" s="213"/>
+      <c r="C26" s="213"/>
+      <c r="D26" s="213"/>
+      <c r="E26" s="213"/>
+      <c r="F26" s="213"/>
+      <c r="G26" s="213"/>
+      <c r="H26" s="213"/>
+      <c r="I26" s="214"/>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="206"/>
-      <c r="B27" s="207"/>
-      <c r="C27" s="207"/>
-      <c r="D27" s="207"/>
-      <c r="E27" s="207"/>
-      <c r="F27" s="207"/>
-      <c r="G27" s="207"/>
-      <c r="H27" s="207"/>
-      <c r="I27" s="208"/>
+      <c r="A27" s="212"/>
+      <c r="B27" s="213"/>
+      <c r="C27" s="213"/>
+      <c r="D27" s="213"/>
+      <c r="E27" s="213"/>
+      <c r="F27" s="213"/>
+      <c r="G27" s="213"/>
+      <c r="H27" s="213"/>
+      <c r="I27" s="214"/>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="206"/>
-      <c r="B28" s="207"/>
-      <c r="C28" s="207"/>
-      <c r="D28" s="207"/>
-      <c r="E28" s="207"/>
-      <c r="F28" s="207"/>
-      <c r="G28" s="207"/>
-      <c r="H28" s="207"/>
-      <c r="I28" s="208"/>
+      <c r="A28" s="212"/>
+      <c r="B28" s="213"/>
+      <c r="C28" s="213"/>
+      <c r="D28" s="213"/>
+      <c r="E28" s="213"/>
+      <c r="F28" s="213"/>
+      <c r="G28" s="213"/>
+      <c r="H28" s="213"/>
+      <c r="I28" s="214"/>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="206"/>
-      <c r="B29" s="207"/>
-      <c r="C29" s="207"/>
-      <c r="D29" s="207"/>
-      <c r="E29" s="207"/>
-      <c r="F29" s="207"/>
-      <c r="G29" s="207"/>
-      <c r="H29" s="207"/>
-      <c r="I29" s="208"/>
+      <c r="A29" s="212"/>
+      <c r="B29" s="213"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="214"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="206"/>
-      <c r="B30" s="207"/>
-      <c r="C30" s="207"/>
-      <c r="D30" s="207"/>
-      <c r="E30" s="207"/>
-      <c r="F30" s="207"/>
-      <c r="G30" s="207"/>
-      <c r="H30" s="207"/>
-      <c r="I30" s="208"/>
+      <c r="A30" s="212"/>
+      <c r="B30" s="213"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="214"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="206"/>
-      <c r="B31" s="207"/>
-      <c r="C31" s="207"/>
-      <c r="D31" s="207"/>
-      <c r="E31" s="207"/>
-      <c r="F31" s="207"/>
-      <c r="G31" s="207"/>
-      <c r="H31" s="207"/>
-      <c r="I31" s="208"/>
+      <c r="A31" s="212"/>
+      <c r="B31" s="213"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="214"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="206"/>
-      <c r="B32" s="207"/>
-      <c r="C32" s="207"/>
-      <c r="D32" s="207"/>
-      <c r="E32" s="207"/>
-      <c r="F32" s="207"/>
-      <c r="G32" s="207"/>
-      <c r="H32" s="207"/>
-      <c r="I32" s="208"/>
+      <c r="A32" s="212"/>
+      <c r="B32" s="213"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="214"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="206"/>
-      <c r="B33" s="207"/>
-      <c r="C33" s="207"/>
-      <c r="D33" s="207"/>
-      <c r="E33" s="207"/>
-      <c r="F33" s="207"/>
-      <c r="G33" s="207"/>
-      <c r="H33" s="207"/>
-      <c r="I33" s="208"/>
-      <c r="L33" s="64"/>
+      <c r="A33" s="212"/>
+      <c r="B33" s="213"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="214"/>
+      <c r="L33" s="62"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="206"/>
-      <c r="B34" s="207"/>
-      <c r="C34" s="207"/>
-      <c r="D34" s="207"/>
-      <c r="E34" s="207"/>
-      <c r="F34" s="207"/>
-      <c r="G34" s="207"/>
-      <c r="H34" s="207"/>
-      <c r="I34" s="208"/>
+      <c r="A34" s="212"/>
+      <c r="B34" s="213"/>
+      <c r="C34" s="213"/>
+      <c r="D34" s="213"/>
+      <c r="E34" s="213"/>
+      <c r="F34" s="213"/>
+      <c r="G34" s="213"/>
+      <c r="H34" s="213"/>
+      <c r="I34" s="214"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="206"/>
-      <c r="B35" s="207"/>
-      <c r="C35" s="207"/>
-      <c r="D35" s="207"/>
-      <c r="E35" s="207"/>
-      <c r="F35" s="207"/>
-      <c r="G35" s="207"/>
-      <c r="H35" s="207"/>
-      <c r="I35" s="208"/>
+      <c r="A35" s="212"/>
+      <c r="B35" s="213"/>
+      <c r="C35" s="213"/>
+      <c r="D35" s="213"/>
+      <c r="E35" s="213"/>
+      <c r="F35" s="213"/>
+      <c r="G35" s="213"/>
+      <c r="H35" s="213"/>
+      <c r="I35" s="214"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="206"/>
-      <c r="B36" s="207"/>
-      <c r="C36" s="207"/>
-      <c r="D36" s="207"/>
-      <c r="E36" s="207"/>
-      <c r="F36" s="207"/>
-      <c r="G36" s="207"/>
-      <c r="H36" s="207"/>
-      <c r="I36" s="208"/>
+      <c r="A36" s="212"/>
+      <c r="B36" s="213"/>
+      <c r="C36" s="213"/>
+      <c r="D36" s="213"/>
+      <c r="E36" s="213"/>
+      <c r="F36" s="213"/>
+      <c r="G36" s="213"/>
+      <c r="H36" s="213"/>
+      <c r="I36" s="214"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="206"/>
-      <c r="B37" s="207"/>
-      <c r="C37" s="207"/>
-      <c r="D37" s="207"/>
-      <c r="E37" s="207"/>
-      <c r="F37" s="207"/>
-      <c r="G37" s="207"/>
-      <c r="H37" s="207"/>
-      <c r="I37" s="208"/>
+      <c r="A37" s="212"/>
+      <c r="B37" s="213"/>
+      <c r="C37" s="213"/>
+      <c r="D37" s="213"/>
+      <c r="E37" s="213"/>
+      <c r="F37" s="213"/>
+      <c r="G37" s="213"/>
+      <c r="H37" s="213"/>
+      <c r="I37" s="214"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="206"/>
-      <c r="B38" s="207"/>
-      <c r="C38" s="207"/>
-      <c r="D38" s="207"/>
-      <c r="E38" s="207"/>
-      <c r="F38" s="207"/>
-      <c r="G38" s="207"/>
-      <c r="H38" s="207"/>
-      <c r="I38" s="208"/>
+      <c r="A38" s="212"/>
+      <c r="B38" s="213"/>
+      <c r="C38" s="213"/>
+      <c r="D38" s="213"/>
+      <c r="E38" s="213"/>
+      <c r="F38" s="213"/>
+      <c r="G38" s="213"/>
+      <c r="H38" s="213"/>
+      <c r="I38" s="214"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="206"/>
-      <c r="B39" s="207"/>
-      <c r="C39" s="207"/>
-      <c r="D39" s="207"/>
-      <c r="E39" s="207"/>
-      <c r="F39" s="207"/>
-      <c r="G39" s="207"/>
-      <c r="H39" s="207"/>
-      <c r="I39" s="208"/>
+      <c r="A39" s="212"/>
+      <c r="B39" s="213"/>
+      <c r="C39" s="213"/>
+      <c r="D39" s="213"/>
+      <c r="E39" s="213"/>
+      <c r="F39" s="213"/>
+      <c r="G39" s="213"/>
+      <c r="H39" s="213"/>
+      <c r="I39" s="214"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="206"/>
-      <c r="B40" s="207"/>
-      <c r="C40" s="207"/>
-      <c r="D40" s="207"/>
-      <c r="E40" s="207"/>
-      <c r="F40" s="207"/>
-      <c r="G40" s="207"/>
-      <c r="H40" s="207"/>
-      <c r="I40" s="208"/>
+      <c r="A40" s="212"/>
+      <c r="B40" s="213"/>
+      <c r="C40" s="213"/>
+      <c r="D40" s="213"/>
+      <c r="E40" s="213"/>
+      <c r="F40" s="213"/>
+      <c r="G40" s="213"/>
+      <c r="H40" s="213"/>
+      <c r="I40" s="214"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="206"/>
-      <c r="B41" s="207"/>
-      <c r="C41" s="207"/>
-      <c r="D41" s="207"/>
-      <c r="E41" s="207"/>
-      <c r="F41" s="207"/>
-      <c r="G41" s="207"/>
-      <c r="H41" s="207"/>
-      <c r="I41" s="208"/>
+      <c r="A41" s="212"/>
+      <c r="B41" s="213"/>
+      <c r="C41" s="213"/>
+      <c r="D41" s="213"/>
+      <c r="E41" s="213"/>
+      <c r="F41" s="213"/>
+      <c r="G41" s="213"/>
+      <c r="H41" s="213"/>
+      <c r="I41" s="214"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="206"/>
-      <c r="B42" s="207"/>
-      <c r="C42" s="207"/>
-      <c r="D42" s="207"/>
-      <c r="E42" s="207"/>
-      <c r="F42" s="207"/>
-      <c r="G42" s="207"/>
-      <c r="H42" s="207"/>
-      <c r="I42" s="208"/>
+      <c r="A42" s="212"/>
+      <c r="B42" s="213"/>
+      <c r="C42" s="213"/>
+      <c r="D42" s="213"/>
+      <c r="E42" s="213"/>
+      <c r="F42" s="213"/>
+      <c r="G42" s="213"/>
+      <c r="H42" s="213"/>
+      <c r="I42" s="214"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="206"/>
-      <c r="B43" s="207"/>
-      <c r="C43" s="207"/>
-      <c r="D43" s="207"/>
-      <c r="E43" s="207"/>
-      <c r="F43" s="207"/>
-      <c r="G43" s="207"/>
-      <c r="H43" s="207"/>
-      <c r="I43" s="208"/>
+      <c r="A43" s="212"/>
+      <c r="B43" s="213"/>
+      <c r="C43" s="213"/>
+      <c r="D43" s="213"/>
+      <c r="E43" s="213"/>
+      <c r="F43" s="213"/>
+      <c r="G43" s="213"/>
+      <c r="H43" s="213"/>
+      <c r="I43" s="214"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="206"/>
-      <c r="B44" s="207"/>
-      <c r="C44" s="207"/>
-      <c r="D44" s="207"/>
-      <c r="E44" s="207"/>
-      <c r="F44" s="207"/>
-      <c r="G44" s="207"/>
-      <c r="H44" s="207"/>
-      <c r="I44" s="208"/>
+      <c r="A44" s="212"/>
+      <c r="B44" s="213"/>
+      <c r="C44" s="213"/>
+      <c r="D44" s="213"/>
+      <c r="E44" s="213"/>
+      <c r="F44" s="213"/>
+      <c r="G44" s="213"/>
+      <c r="H44" s="213"/>
+      <c r="I44" s="214"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="206"/>
-      <c r="B45" s="207"/>
-      <c r="C45" s="207"/>
-      <c r="D45" s="207"/>
-      <c r="E45" s="207"/>
-      <c r="F45" s="207"/>
-      <c r="G45" s="207"/>
-      <c r="H45" s="207"/>
-      <c r="I45" s="208"/>
+      <c r="A45" s="212"/>
+      <c r="B45" s="213"/>
+      <c r="C45" s="213"/>
+      <c r="D45" s="213"/>
+      <c r="E45" s="213"/>
+      <c r="F45" s="213"/>
+      <c r="G45" s="213"/>
+      <c r="H45" s="213"/>
+      <c r="I45" s="214"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="224"/>
-      <c r="B46" s="225"/>
-      <c r="C46" s="225"/>
-      <c r="D46" s="225"/>
-      <c r="E46" s="225"/>
-      <c r="F46" s="225"/>
-      <c r="G46" s="225"/>
-      <c r="H46" s="225"/>
-      <c r="I46" s="226"/>
+      <c r="A46" s="239"/>
+      <c r="B46" s="240"/>
+      <c r="C46" s="240"/>
+      <c r="D46" s="240"/>
+      <c r="E46" s="240"/>
+      <c r="F46" s="240"/>
+      <c r="G46" s="240"/>
+      <c r="H46" s="240"/>
+      <c r="I46" s="241"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="37">
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A42:I42"/>
@@ -4225,20 +4263,22 @@
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A39:I39"/>
     <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A16:I16"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A12:I13"/>
-    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A14:I15"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A11:I12"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A9:I10"/>
+    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A27:I27"/>
@@ -4257,360 +4297,369 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F52ED7-B55C-4544-B1B9-4049608F227A}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="241" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="243"/>
-      <c r="E1" s="236" t="s">
+    <row r="1" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="257" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="263" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="264"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="227" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="228"/>
+      <c r="C2" s="228"/>
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="228"/>
+      <c r="H2" s="228"/>
+      <c r="I2" s="229"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="251" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="252"/>
+      <c r="C3" s="252"/>
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="252"/>
+      <c r="H3" s="252"/>
+      <c r="I3" s="253"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="254" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="255"/>
+      <c r="C4" s="255"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="256"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="51"/>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="89"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="221" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="222"/>
+      <c r="C7" s="222"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="223"/>
+    </row>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="242" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="243"/>
+      <c r="C8" s="243"/>
+      <c r="D8" s="243"/>
+      <c r="E8" s="243"/>
+      <c r="F8" s="243"/>
+      <c r="G8" s="243"/>
+      <c r="H8" s="243"/>
+      <c r="I8" s="244"/>
+    </row>
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="245"/>
+      <c r="B9" s="246"/>
+      <c r="C9" s="246"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="247"/>
+    </row>
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="58"/>
+    </row>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="215" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="216"/>
+      <c r="C11" s="216"/>
+      <c r="D11" s="216"/>
+      <c r="E11" s="216"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="216"/>
+      <c r="H11" s="216"/>
+      <c r="I11" s="217"/>
+    </row>
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="215"/>
+      <c r="B12" s="216"/>
+      <c r="C12" s="216"/>
+      <c r="D12" s="216"/>
+      <c r="E12" s="216"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="216"/>
+      <c r="H12" s="216"/>
+      <c r="I12" s="217"/>
+    </row>
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="233" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="234"/>
+      <c r="C13" s="234"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="234"/>
+      <c r="G13" s="234"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="235"/>
+    </row>
+    <row r="14" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="248" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="249"/>
+      <c r="C14" s="249"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="250"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="260" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="261"/>
+      <c r="C16" s="261"/>
+      <c r="D16" s="262"/>
+      <c r="E16" s="265" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="266"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="227" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="228"/>
+      <c r="C17" s="228"/>
+      <c r="D17" s="228"/>
+      <c r="E17" s="228"/>
+      <c r="F17" s="228"/>
+      <c r="G17" s="228"/>
+      <c r="H17" s="228"/>
+      <c r="I17" s="229"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="251" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="252"/>
+      <c r="C18" s="252"/>
+      <c r="D18" s="252"/>
+      <c r="E18" s="252"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="252"/>
+      <c r="H18" s="252"/>
+      <c r="I18" s="253"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="254" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="255"/>
+      <c r="C19" s="255"/>
+      <c r="D19" s="255"/>
+      <c r="E19" s="255"/>
+      <c r="F19" s="255"/>
+      <c r="G19" s="255"/>
+      <c r="H19" s="255"/>
+      <c r="I19" s="256"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="51"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="51"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="48"/>
+    </row>
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="215" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="237"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="221" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="222"/>
-      <c r="C2" s="222"/>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
-      <c r="G2" s="222"/>
-      <c r="H2" s="222"/>
-      <c r="I2" s="223"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="244" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="245"/>
-      <c r="C3" s="245"/>
-      <c r="D3" s="245"/>
-      <c r="E3" s="245"/>
-      <c r="F3" s="245"/>
-      <c r="G3" s="245"/>
-      <c r="H3" s="245"/>
-      <c r="I3" s="246"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="247" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="248"/>
-      <c r="C4" s="248"/>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="249"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="52"/>
-    </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="52"/>
-    </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="233" t="s">
+      <c r="B23" s="216"/>
+      <c r="C23" s="216"/>
+      <c r="D23" s="216"/>
+      <c r="E23" s="216"/>
+      <c r="F23" s="216"/>
+      <c r="G23" s="216"/>
+      <c r="H23" s="216"/>
+      <c r="I23" s="217"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="233" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="234"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="234"/>
+      <c r="I24" s="235"/>
+    </row>
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="230" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="234"/>
-      <c r="C7" s="234"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="234"/>
-      <c r="F7" s="234"/>
-      <c r="G7" s="234"/>
-      <c r="H7" s="234"/>
-      <c r="I7" s="235"/>
-    </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="230" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="231"/>
-      <c r="C8" s="231"/>
-      <c r="D8" s="231"/>
-      <c r="E8" s="231"/>
-      <c r="F8" s="231"/>
-      <c r="G8" s="231"/>
-      <c r="H8" s="231"/>
-      <c r="I8" s="232"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="247" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="248"/>
-      <c r="C9" s="248"/>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="249"/>
-    </row>
-    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="253" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="254"/>
-      <c r="C10" s="254"/>
-      <c r="D10" s="254"/>
-      <c r="E10" s="254"/>
-      <c r="F10" s="254"/>
-      <c r="G10" s="254"/>
-      <c r="H10" s="254"/>
-      <c r="I10" s="255"/>
-    </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="65"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="60"/>
-    </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="227" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="228"/>
-      <c r="C12" s="228"/>
-      <c r="D12" s="228"/>
-      <c r="E12" s="228"/>
-      <c r="F12" s="228"/>
-      <c r="G12" s="228"/>
-      <c r="H12" s="228"/>
-      <c r="I12" s="229"/>
-    </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="238"/>
-      <c r="B13" s="239"/>
-      <c r="C13" s="239"/>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="240"/>
-    </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="250" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="251"/>
-      <c r="C15" s="251"/>
-      <c r="D15" s="252"/>
-      <c r="E15" s="236" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="237"/>
-    </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="221" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="222"/>
-      <c r="C16" s="222"/>
-      <c r="D16" s="222"/>
-      <c r="E16" s="222"/>
-      <c r="F16" s="222"/>
-      <c r="G16" s="222"/>
-      <c r="H16" s="222"/>
-      <c r="I16" s="223"/>
-      <c r="K16" s="64"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="244" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="245"/>
-      <c r="C17" s="245"/>
-      <c r="D17" s="245"/>
-      <c r="E17" s="245"/>
-      <c r="F17" s="245"/>
-      <c r="G17" s="245"/>
-      <c r="H17" s="245"/>
-      <c r="I17" s="246"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="247" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="248"/>
-      <c r="C18" s="248"/>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="249"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="52"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="52"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="48"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="227" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="228"/>
-      <c r="C22" s="228"/>
-      <c r="D22" s="228"/>
-      <c r="E22" s="228"/>
-      <c r="F22" s="228"/>
-      <c r="G22" s="228"/>
-      <c r="H22" s="228"/>
-      <c r="I22" s="229"/>
-    </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="233" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="234"/>
-      <c r="C23" s="234"/>
-      <c r="D23" s="234"/>
-      <c r="E23" s="234"/>
-      <c r="F23" s="234"/>
-      <c r="G23" s="234"/>
-      <c r="H23" s="234"/>
-      <c r="I23" s="235"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="230" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="231"/>
-      <c r="C24" s="231"/>
-      <c r="D24" s="231"/>
-      <c r="E24" s="231"/>
-      <c r="F24" s="231"/>
-      <c r="G24" s="231"/>
-      <c r="H24" s="231"/>
-      <c r="I24" s="232"/>
-    </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="63"/>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="238" t="s">
-        <v>90</v>
-      </c>
-      <c r="B26" s="239"/>
-      <c r="C26" s="239"/>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="240"/>
-    </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B25" s="231"/>
+      <c r="C25" s="231"/>
+      <c r="D25" s="231"/>
+      <c r="E25" s="231"/>
+      <c r="F25" s="231"/>
+      <c r="G25" s="231"/>
+      <c r="H25" s="231"/>
+      <c r="I25" s="232"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="61"/>
+    </row>
+    <row r="27" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="248" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="249"/>
+      <c r="C27" s="249"/>
+      <c r="D27" s="249"/>
+      <c r="E27" s="249"/>
+      <c r="F27" s="249"/>
+      <c r="G27" s="249"/>
+      <c r="H27" s="249"/>
+      <c r="I27" s="250"/>
+    </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A12:I13"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A11:I12"/>
     <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A8:I9"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4640,36 +4689,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="261" t="s">
+      <c r="A1" s="267" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="262"/>
-      <c r="C1" s="256"/>
-      <c r="E1" s="261" t="s">
+      <c r="B1" s="268"/>
+      <c r="C1" s="269"/>
+      <c r="E1" s="267" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="262"/>
-      <c r="G1" s="256"/>
+      <c r="F1" s="268"/>
+      <c r="G1" s="269"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="76" t="s">
+      <c r="G2" s="72" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="5">
@@ -4681,22 +4730,22 @@
       <c r="E3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="78">
-        <v>0</v>
+      <c r="F3" s="74">
+        <v>1</v>
       </c>
       <c r="G3" s="9">
         <v>0</v>
       </c>
-      <c r="J3" s="64"/>
-      <c r="N3" s="258" t="s">
+      <c r="J3" s="62"/>
+      <c r="N3" s="271" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="256" t="s">
+      <c r="O3" s="269" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="73" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="5">
@@ -4715,11 +4764,11 @@
         <v>0</v>
       </c>
       <c r="M4" s="20"/>
-      <c r="N4" s="259"/>
-      <c r="O4" s="257"/>
+      <c r="N4" s="272"/>
+      <c r="O4" s="270"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="73" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="5">
@@ -4729,9 +4778,9 @@
         <v>0</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="80"/>
+      <c r="F5" s="76"/>
       <c r="G5" s="14"/>
-      <c r="I5" s="79"/>
+      <c r="I5" s="75"/>
       <c r="J5" s="15" t="s">
         <v>9</v>
       </c>
@@ -4749,7 +4798,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="77" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11">
@@ -4759,9 +4808,9 @@
         <v>0</v>
       </c>
       <c r="E6" s="13"/>
-      <c r="F6" s="80"/>
+      <c r="F6" s="76"/>
       <c r="G6" s="14"/>
-      <c r="I6" s="82" t="s">
+      <c r="I6" s="78" t="s">
         <v>7</v>
       </c>
       <c r="J6" s="19">
@@ -4781,7 +4830,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="79" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="8">
@@ -4801,7 +4850,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="80" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="12">
@@ -4821,32 +4870,32 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="85"/>
+      <c r="A11" s="81"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="85"/>
+      <c r="A12" s="81"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="260" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" s="260"/>
-      <c r="C25" s="260"/>
-      <c r="D25" s="260"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="260"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="260"/>
-      <c r="I25" s="260"/>
+      <c r="A25" s="273" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="273"/>
+      <c r="C25" s="273"/>
+      <c r="D25" s="273"/>
+      <c r="E25" s="273"/>
+      <c r="F25" s="273"/>
+      <c r="G25" s="273"/>
+      <c r="H25" s="273"/>
+      <c r="I25" s="273"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="233" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B26" s="234"/>
       <c r="C26" s="234"/>
@@ -4859,7 +4908,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="230" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B27" s="231"/>
       <c r="C27" s="231"/>
@@ -4872,23 +4921,23 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K29" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K30" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A27:I27"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6" xr:uid="{E1FA2264-B5F6-4549-B0D7-4D2128963B76}">
